--- a/backend/uploads/plantilla_clientes.xlsx
+++ b/backend/uploads/plantilla_clientes.xlsx
@@ -452,10 +452,10 @@
         <v>Juan Pérez García</v>
       </c>
       <c r="B2" t="str">
-        <v>961-123-4567</v>
+        <v>9611234567</v>
       </c>
       <c r="C2" t="str">
-        <v>961-123-4568</v>
+        <v>9611234568</v>
       </c>
       <c r="D2" t="str">
         <v>juan.perez@email.com</v>
@@ -470,7 +470,7 @@
         <v>PEGJ850315ABC</v>
       </c>
       <c r="H2" t="str">
-        <v>612 - Personas Físicas con Actividades Empresariales</v>
+        <v>612</v>
       </c>
       <c r="I2" t="str">
         <v>Av. Central 123, Col. Centro, Tuxtla Gutiérrez, Chiapas</v>
@@ -479,7 +479,7 @@
         <v>29000</v>
       </c>
       <c r="K2" t="str">
-        <v>G03 - Gastos en general</v>
+        <v>G03</v>
       </c>
     </row>
     <row r="3">
@@ -487,13 +487,13 @@
         <v>Comercializadora López S.A. de C.V.</v>
       </c>
       <c r="B3" t="str">
-        <v>961-234-5678</v>
+        <v>9612345678</v>
       </c>
       <c r="C3" t="str">
         <v/>
       </c>
       <c r="D3" t="str">
-        <v>contacto@lopez.com.mx</v>
+        <v/>
       </c>
       <c r="E3" t="str">
         <v>Blvd. Belisario Domínguez 456, Col. Moctezuma, Tuxtla Gutiérrez, Chiapas</v>
@@ -505,7 +505,7 @@
         <v>CLS920810XYZ</v>
       </c>
       <c r="H3" t="str">
-        <v>601 - General de Ley Personas Morales</v>
+        <v>601</v>
       </c>
       <c r="I3" t="str">
         <v>Blvd. Belisario Domínguez 456, Col. Moctezuma, Tuxtla Gutiérrez, Chiapas</v>
@@ -514,7 +514,7 @@
         <v>29030</v>
       </c>
       <c r="K3" t="str">
-        <v>G01 - Adquisición de mercancías</v>
+        <v>G01</v>
       </c>
     </row>
     <row r="4">
@@ -522,10 +522,10 @@
         <v>María González Hernández</v>
       </c>
       <c r="B4" t="str">
-        <v>967-345-6789</v>
+        <v>9673456789</v>
       </c>
       <c r="C4" t="str">
-        <v>967-345-6790</v>
+        <v>9673456790</v>
       </c>
       <c r="D4" t="str">
         <v>maria.gonzalez@email.com</v>
@@ -540,7 +540,7 @@
         <v>GOHM750425DEF</v>
       </c>
       <c r="H4" t="str">
-        <v>612 - Personas Físicas con Actividades Empresariales</v>
+        <v>612</v>
       </c>
       <c r="I4" t="str">
         <v>Real de Guadalupe 789, Centro, San Cristóbal de las Casas, Chiapas</v>
@@ -549,7 +549,7 @@
         <v>29200</v>
       </c>
       <c r="K4" t="str">
-        <v>G03 - Gastos en general</v>
+        <v>G03</v>
       </c>
     </row>
   </sheetData>

--- a/backend/uploads/plantilla_clientes.xlsx
+++ b/backend/uploads/plantilla_clientes.xlsx
@@ -407,7 +407,7 @@
     <col min="6" max="6" width="30.83203125" customWidth="1"/>
     <col min="7" max="7" width="15.83203125" customWidth="1"/>
     <col min="8" max="8" width="40.83203125" customWidth="1"/>
-    <col min="9" max="9" width="40.83203125" customWidth="1"/>
+    <col min="9" max="9" width="50.83203125" customWidth="1"/>
     <col min="10" max="10" width="12.83203125" customWidth="1"/>
     <col min="11" max="11" width="35.83203125" customWidth="1"/>
   </cols>
@@ -438,7 +438,7 @@
         <v>regimen fiscal</v>
       </c>
       <c r="I1" t="str">
-        <v>direccion</v>
+        <v>direccion de facturacion</v>
       </c>
       <c r="J1" t="str">
         <v>codigo postal</v>
@@ -461,7 +461,7 @@
         <v>juan.perez@email.com</v>
       </c>
       <c r="E2" t="str">
-        <v>Av. Central 123, Col. Centro, Tuxtla Gutiérrez, Chiapas</v>
+        <v>Av. Central 123, Local 5, Col. Centro, Tuxtla Gutiérrez, Chiapas</v>
       </c>
       <c r="F2" t="str">
         <v>Juan Pérez García</v>
@@ -496,7 +496,7 @@
         <v/>
       </c>
       <c r="E3" t="str">
-        <v>Blvd. Belisario Domínguez 456, Col. Moctezuma, Tuxtla Gutiérrez, Chiapas</v>
+        <v>Bodega 3, Parque Industrial, Tuxtla Gutiérrez, Chiapas</v>
       </c>
       <c r="F3" t="str">
         <v>Comercializadora López S.A. de C.V.</v>

--- a/backend/uploads/plantilla_clientes.xlsx
+++ b/backend/uploads/plantilla_clientes.xlsx
@@ -1,55 +1,420 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <workbookPr codeName="ThisWorkbook"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
+  <bookViews>
+    <workbookView xWindow="0" yWindow="0" windowWidth="12000" windowHeight="24000" firstSheet="0" activeTab="2"/>
+  </bookViews>
   <sheets>
-    <sheet name="Clientes" sheetId="1" r:id="rId1"/>
+    <sheet sheetId="1" name="Regimenes Fiscales" state="visible" r:id="rId4"/>
+    <sheet sheetId="2" name="Usos CFDI" state="visible" r:id="rId5"/>
+    <sheet sheetId="3" name="Clientes" state="visible" r:id="rId6"/>
   </sheets>
+  <calcPr calcId="171027"/>
 </workbook>
 </file>
 
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="1">
-    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLDAPR" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
-          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <cellMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </cellMetadata>
-</metadata>
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="123">
+  <si>
+    <t>Código</t>
+  </si>
+  <si>
+    <t>Descripción</t>
+  </si>
+  <si>
+    <t>601</t>
+  </si>
+  <si>
+    <t>General de Ley Personas Morales</t>
+  </si>
+  <si>
+    <t>603</t>
+  </si>
+  <si>
+    <t>Personas Morales con Fines no Lucrativos</t>
+  </si>
+  <si>
+    <t>605</t>
+  </si>
+  <si>
+    <t>Sueldos y Salarios e Ingresos Asimilados a Salarios</t>
+  </si>
+  <si>
+    <t>606</t>
+  </si>
+  <si>
+    <t>Arrendamiento</t>
+  </si>
+  <si>
+    <t>607</t>
+  </si>
+  <si>
+    <t>Régimen de Enajenación o Adquisición de Bienes</t>
+  </si>
+  <si>
+    <t>608</t>
+  </si>
+  <si>
+    <t>Demás ingresos</t>
+  </si>
+  <si>
+    <t>610</t>
+  </si>
+  <si>
+    <t>Residentes en el Extranjero sin Establecimiento Permanente en México</t>
+  </si>
+  <si>
+    <t>611</t>
+  </si>
+  <si>
+    <t>Ingresos por Dividendos (socios y accionistas)</t>
+  </si>
+  <si>
+    <t>612</t>
+  </si>
+  <si>
+    <t>Personas Físicas con Actividades Empresariales y Profesionales</t>
+  </si>
+  <si>
+    <t>614</t>
+  </si>
+  <si>
+    <t>Ingresos por intereses</t>
+  </si>
+  <si>
+    <t>615</t>
+  </si>
+  <si>
+    <t>Régimen de los ingresos por obtención de premios</t>
+  </si>
+  <si>
+    <t>616</t>
+  </si>
+  <si>
+    <t>Sin obligaciones fiscales</t>
+  </si>
+  <si>
+    <t>620</t>
+  </si>
+  <si>
+    <t>Sociedades Cooperativas de Producción que optan por diferir sus ingresos</t>
+  </si>
+  <si>
+    <t>621</t>
+  </si>
+  <si>
+    <t>Incorporación Fiscal</t>
+  </si>
+  <si>
+    <t>622</t>
+  </si>
+  <si>
+    <t>Actividades Agrícolas, Ganaderas, Silvícolas y Pesqueras</t>
+  </si>
+  <si>
+    <t>623</t>
+  </si>
+  <si>
+    <t>Opcional para Grupos de Sociedades</t>
+  </si>
+  <si>
+    <t>624</t>
+  </si>
+  <si>
+    <t>Coordinados</t>
+  </si>
+  <si>
+    <t>625</t>
+  </si>
+  <si>
+    <t>Régimen de las Actividades Empresariales con ingresos a través de Plataformas Tecnológicas</t>
+  </si>
+  <si>
+    <t>626</t>
+  </si>
+  <si>
+    <t>Régimen Simplificado de Confianza</t>
+  </si>
+  <si>
+    <t>CN01</t>
+  </si>
+  <si>
+    <t>Nómina</t>
+  </si>
+  <si>
+    <t>CP01</t>
+  </si>
+  <si>
+    <t>Pagos</t>
+  </si>
+  <si>
+    <t>D01</t>
+  </si>
+  <si>
+    <t>Honorarios médicos, dentales y gastos hospitalarios</t>
+  </si>
+  <si>
+    <t>D02</t>
+  </si>
+  <si>
+    <t>Gastos médicos por incapacidad o discapacidad</t>
+  </si>
+  <si>
+    <t>D03</t>
+  </si>
+  <si>
+    <t>Gastos funerales</t>
+  </si>
+  <si>
+    <t>D04</t>
+  </si>
+  <si>
+    <t>Donativos</t>
+  </si>
+  <si>
+    <t>D05</t>
+  </si>
+  <si>
+    <t>Intereses reales efectivamente pagados por créditos hipotecarios</t>
+  </si>
+  <si>
+    <t>D06</t>
+  </si>
+  <si>
+    <t>Aportaciones voluntarias al SAR</t>
+  </si>
+  <si>
+    <t>D07</t>
+  </si>
+  <si>
+    <t>Primas por seguros de gastos médicos</t>
+  </si>
+  <si>
+    <t>D08</t>
+  </si>
+  <si>
+    <t>Gastos de transportación escolar obligatoria</t>
+  </si>
+  <si>
+    <t>D09</t>
+  </si>
+  <si>
+    <t>Depósitos en cuentas para el ahorro, primas que tengan como base planes de pensiones</t>
+  </si>
+  <si>
+    <t>D10</t>
+  </si>
+  <si>
+    <t>Pagos por servicios educativos (colegiaturas)</t>
+  </si>
+  <si>
+    <t>G01</t>
+  </si>
+  <si>
+    <t>Adquisición de mercancías</t>
+  </si>
+  <si>
+    <t>G02</t>
+  </si>
+  <si>
+    <t>Devoluciones, descuentos o bonificaciones</t>
+  </si>
+  <si>
+    <t>G03</t>
+  </si>
+  <si>
+    <t>Gastos en general</t>
+  </si>
+  <si>
+    <t>I01</t>
+  </si>
+  <si>
+    <t>Construcciones</t>
+  </si>
+  <si>
+    <t>I02</t>
+  </si>
+  <si>
+    <t>Mobiliario y equipo de oficina por inversiones</t>
+  </si>
+  <si>
+    <t>I03</t>
+  </si>
+  <si>
+    <t>Equipo de transporte</t>
+  </si>
+  <si>
+    <t>I04</t>
+  </si>
+  <si>
+    <t>Equipo de cómputo y accesorios</t>
+  </si>
+  <si>
+    <t>I05</t>
+  </si>
+  <si>
+    <t>Dados, troqueles, moldes, matrices y herramental</t>
+  </si>
+  <si>
+    <t>I06</t>
+  </si>
+  <si>
+    <t>Comunicaciones telefónicas</t>
+  </si>
+  <si>
+    <t>I07</t>
+  </si>
+  <si>
+    <t>Comunicaciones satelitales</t>
+  </si>
+  <si>
+    <t>I08</t>
+  </si>
+  <si>
+    <t>Otra maquinaria y equipo</t>
+  </si>
+  <si>
+    <t>S01</t>
+  </si>
+  <si>
+    <t>Sin efectos fiscales</t>
+  </si>
+  <si>
+    <t>nombre</t>
+  </si>
+  <si>
+    <t>telefono</t>
+  </si>
+  <si>
+    <t>segundo telefono</t>
+  </si>
+  <si>
+    <t>correo</t>
+  </si>
+  <si>
+    <t>segundo correo</t>
+  </si>
+  <si>
+    <t>direccion de entrega</t>
+  </si>
+  <si>
+    <t>razon social</t>
+  </si>
+  <si>
+    <t>rfc</t>
+  </si>
+  <si>
+    <t>regimen fiscal</t>
+  </si>
+  <si>
+    <t>direccion de facturacion</t>
+  </si>
+  <si>
+    <t>codigo postal</t>
+  </si>
+  <si>
+    <t>uso cfdi</t>
+  </si>
+  <si>
+    <t>Juan Pérez García</t>
+  </si>
+  <si>
+    <t>9611234567</t>
+  </si>
+  <si>
+    <t>9611234568</t>
+  </si>
+  <si>
+    <t>juan.perez@email.com</t>
+  </si>
+  <si>
+    <t>juan.alt@email.com</t>
+  </si>
+  <si>
+    <t>Av. Central 123, Local 5, Col. Centro, Tuxtla Gutiérrez, Chiapas</t>
+  </si>
+  <si>
+    <t>PEGJ850315ABC</t>
+  </si>
+  <si>
+    <t>Av. Central 123, Col. Centro, Tuxtla Gutiérrez, Chiapas</t>
+  </si>
+  <si>
+    <t>29000</t>
+  </si>
+  <si>
+    <t>Comercializadora López S.A. de C.V.</t>
+  </si>
+  <si>
+    <t>9612345678</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>Bodega 3, Parque Industrial, Tuxtla Gutiérrez, Chiapas</t>
+  </si>
+  <si>
+    <t>CLS920810XYZ</t>
+  </si>
+  <si>
+    <t>Blvd. Belisario Domínguez 456, Col. Moctezuma, Tuxtla Gutiérrez, Chiapas</t>
+  </si>
+  <si>
+    <t>29030</t>
+  </si>
+  <si>
+    <t>María González Hernández</t>
+  </si>
+  <si>
+    <t>9673456789</t>
+  </si>
+  <si>
+    <t>9673456790</t>
+  </si>
+  <si>
+    <t>maria.gonzalez@email.com</t>
+  </si>
+  <si>
+    <t>Real de Guadalupe 789, Centro, San Cristóbal de las Casas, Chiapas</t>
+  </si>
+  <si>
+    <t>GOHM750425DEF</t>
+  </si>
+  <si>
+    <t>29200</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="1">
-    <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
-  </numFmts>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
-      <sz val="12"/>
       <color theme="1"/>
-      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FFFFFFFF"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F7244"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -64,14 +429,25 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+  <cellXfs count="2">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -396,165 +772,576 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K4"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:B20"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="30.83203125" customWidth="1"/>
-    <col min="2" max="2" width="15.83203125" customWidth="1"/>
-    <col min="3" max="3" width="15.83203125" customWidth="1"/>
-    <col min="4" max="4" width="25.83203125" customWidth="1"/>
-    <col min="5" max="5" width="50.83203125" customWidth="1"/>
-    <col min="6" max="6" width="30.83203125" customWidth="1"/>
-    <col min="7" max="7" width="15.83203125" customWidth="1"/>
-    <col min="8" max="8" width="40.83203125" customWidth="1"/>
-    <col min="9" max="9" width="50.83203125" customWidth="1"/>
-    <col min="10" max="10" width="12.83203125" customWidth="1"/>
-    <col min="11" max="11" width="35.83203125" customWidth="1"/>
+    <col min="1" max="1" width="12" customWidth="1"/>
+    <col min="2" max="2" width="65" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>nombre</v>
-      </c>
-      <c r="B1" t="str">
-        <v>telefono</v>
-      </c>
-      <c r="C1" t="str">
-        <v>segundo telefono</v>
-      </c>
-      <c r="D1" t="str">
-        <v>correo</v>
-      </c>
-      <c r="E1" t="str">
-        <v>direccion de entrega</v>
-      </c>
-      <c r="F1" t="str">
-        <v>razon social</v>
-      </c>
-      <c r="G1" t="str">
-        <v>rfc</v>
-      </c>
-      <c r="H1" t="str">
-        <v>regimen fiscal</v>
-      </c>
-      <c r="I1" t="str">
-        <v>direccion de facturacion</v>
-      </c>
-      <c r="J1" t="str">
-        <v>codigo postal</v>
-      </c>
-      <c r="K1" t="str">
-        <v>uso cfdi</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>Juan Pérez García</v>
-      </c>
-      <c r="B2" t="str">
-        <v>9611234567</v>
-      </c>
-      <c r="C2" t="str">
-        <v>9611234568</v>
-      </c>
-      <c r="D2" t="str">
-        <v>juan.perez@email.com</v>
-      </c>
-      <c r="E2" t="str">
-        <v>Av. Central 123, Local 5, Col. Centro, Tuxtla Gutiérrez, Chiapas</v>
-      </c>
-      <c r="F2" t="str">
-        <v>Juan Pérez García</v>
-      </c>
-      <c r="G2" t="str">
-        <v>PEGJ850315ABC</v>
-      </c>
-      <c r="H2" t="str">
-        <v>612</v>
-      </c>
-      <c r="I2" t="str">
-        <v>Av. Central 123, Col. Centro, Tuxtla Gutiérrez, Chiapas</v>
-      </c>
-      <c r="J2" t="str">
-        <v>29000</v>
-      </c>
-      <c r="K2" t="str">
-        <v>G03</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>Comercializadora López S.A. de C.V.</v>
-      </c>
-      <c r="B3" t="str">
-        <v>9612345678</v>
-      </c>
-      <c r="C3" t="str">
-        <v/>
-      </c>
-      <c r="D3" t="str">
-        <v/>
-      </c>
-      <c r="E3" t="str">
-        <v>Bodega 3, Parque Industrial, Tuxtla Gutiérrez, Chiapas</v>
-      </c>
-      <c r="F3" t="str">
-        <v>Comercializadora López S.A. de C.V.</v>
-      </c>
-      <c r="G3" t="str">
-        <v>CLS920810XYZ</v>
-      </c>
-      <c r="H3" t="str">
-        <v>601</v>
-      </c>
-      <c r="I3" t="str">
-        <v>Blvd. Belisario Domínguez 456, Col. Moctezuma, Tuxtla Gutiérrez, Chiapas</v>
-      </c>
-      <c r="J3" t="str">
-        <v>29030</v>
-      </c>
-      <c r="K3" t="str">
-        <v>G01</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>María González Hernández</v>
-      </c>
-      <c r="B4" t="str">
-        <v>9673456789</v>
-      </c>
-      <c r="C4" t="str">
-        <v>9673456790</v>
-      </c>
-      <c r="D4" t="str">
-        <v>maria.gonzalez@email.com</v>
-      </c>
-      <c r="E4" t="str">
-        <v>Real de Guadalupe 789, Centro, San Cristóbal de las Casas, Chiapas</v>
-      </c>
-      <c r="F4" t="str">
-        <v>María González Hernández</v>
-      </c>
-      <c r="G4" t="str">
-        <v>GOHM750425DEF</v>
-      </c>
-      <c r="H4" t="str">
-        <v>612</v>
-      </c>
-      <c r="I4" t="str">
-        <v>Real de Guadalupe 789, Centro, San Cristóbal de las Casas, Chiapas</v>
-      </c>
-      <c r="J4" t="str">
-        <v>29200</v>
-      </c>
-      <c r="K4" t="str">
-        <v>G03</v>
+    <row r="1" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>12</v>
+      </c>
+      <c r="B7" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>14</v>
+      </c>
+      <c r="B8" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>16</v>
+      </c>
+      <c r="B9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>18</v>
+      </c>
+      <c r="B10" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>20</v>
+      </c>
+      <c r="B11" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>22</v>
+      </c>
+      <c r="B12" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>24</v>
+      </c>
+      <c r="B13" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>26</v>
+      </c>
+      <c r="B14" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>28</v>
+      </c>
+      <c r="B15" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>30</v>
+      </c>
+      <c r="B16" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>32</v>
+      </c>
+      <c r="B17" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>34</v>
+      </c>
+      <c r="B18" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>36</v>
+      </c>
+      <c r="B19" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>38</v>
+      </c>
+      <c r="B20" t="s">
+        <v>39</v>
       </c>
     </row>
   </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:K4"/>
-  </ignoredErrors>
+  <sheetProtection sheet="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:B25"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="12" customWidth="1"/>
+    <col min="2" max="2" width="65" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>40</v>
+      </c>
+      <c r="B2" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B3" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>44</v>
+      </c>
+      <c r="B4" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>46</v>
+      </c>
+      <c r="B5" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>48</v>
+      </c>
+      <c r="B6" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>50</v>
+      </c>
+      <c r="B7" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>52</v>
+      </c>
+      <c r="B8" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>54</v>
+      </c>
+      <c r="B9" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>56</v>
+      </c>
+      <c r="B10" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>58</v>
+      </c>
+      <c r="B11" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>60</v>
+      </c>
+      <c r="B12" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>62</v>
+      </c>
+      <c r="B13" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>64</v>
+      </c>
+      <c r="B14" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>66</v>
+      </c>
+      <c r="B15" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>68</v>
+      </c>
+      <c r="B16" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>70</v>
+      </c>
+      <c r="B17" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>72</v>
+      </c>
+      <c r="B18" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>74</v>
+      </c>
+      <c r="B19" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>76</v>
+      </c>
+      <c r="B20" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>78</v>
+      </c>
+      <c r="B21" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>80</v>
+      </c>
+      <c r="B22" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>82</v>
+      </c>
+      <c r="B23" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>84</v>
+      </c>
+      <c r="B24" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>86</v>
+      </c>
+      <c r="B25" t="s">
+        <v>87</v>
+      </c>
+    </row>
+  </sheetData>
+  <sheetProtection sheet="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:L4"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="32" customWidth="1"/>
+    <col min="2" max="2" width="16" customWidth="1"/>
+    <col min="3" max="3" width="18" customWidth="1"/>
+    <col min="4" max="5" width="28" customWidth="1"/>
+    <col min="6" max="6" width="52" customWidth="1"/>
+    <col min="7" max="7" width="32" customWidth="1"/>
+    <col min="8" max="8" width="16" customWidth="1"/>
+    <col min="9" max="9" width="20" customWidth="1"/>
+    <col min="10" max="10" width="52" customWidth="1"/>
+    <col min="11" max="12" width="14" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="20" customHeight="1" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>100</v>
+      </c>
+      <c r="B2" t="s">
+        <v>101</v>
+      </c>
+      <c r="C2" t="s">
+        <v>102</v>
+      </c>
+      <c r="D2" t="s">
+        <v>103</v>
+      </c>
+      <c r="E2" t="s">
+        <v>104</v>
+      </c>
+      <c r="F2" t="s">
+        <v>105</v>
+      </c>
+      <c r="G2" t="s">
+        <v>100</v>
+      </c>
+      <c r="H2" t="s">
+        <v>106</v>
+      </c>
+      <c r="I2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J2" t="s">
+        <v>107</v>
+      </c>
+      <c r="K2" t="s">
+        <v>108</v>
+      </c>
+      <c r="L2" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>109</v>
+      </c>
+      <c r="B3" t="s">
+        <v>110</v>
+      </c>
+      <c r="C3" t="s">
+        <v>111</v>
+      </c>
+      <c r="D3" t="s">
+        <v>111</v>
+      </c>
+      <c r="E3" t="s">
+        <v>111</v>
+      </c>
+      <c r="F3" t="s">
+        <v>112</v>
+      </c>
+      <c r="G3" t="s">
+        <v>109</v>
+      </c>
+      <c r="H3" t="s">
+        <v>113</v>
+      </c>
+      <c r="I3" t="s">
+        <v>2</v>
+      </c>
+      <c r="J3" t="s">
+        <v>114</v>
+      </c>
+      <c r="K3" t="s">
+        <v>115</v>
+      </c>
+      <c r="L3" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>116</v>
+      </c>
+      <c r="B4" t="s">
+        <v>117</v>
+      </c>
+      <c r="C4" t="s">
+        <v>118</v>
+      </c>
+      <c r="D4" t="s">
+        <v>119</v>
+      </c>
+      <c r="E4" t="s">
+        <v>111</v>
+      </c>
+      <c r="F4" t="s">
+        <v>120</v>
+      </c>
+      <c r="G4" t="s">
+        <v>116</v>
+      </c>
+      <c r="H4" t="s">
+        <v>121</v>
+      </c>
+      <c r="I4" t="s">
+        <v>18</v>
+      </c>
+      <c r="J4" t="s">
+        <v>120</v>
+      </c>
+      <c r="K4" t="s">
+        <v>122</v>
+      </c>
+      <c r="L4" t="s">
+        <v>68</v>
+      </c>
+    </row>
+  </sheetData>
+  <dataValidations count="2">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="error" errorTitle="Régimen Fiscal inválido" error="Seleccione un código de régimen fiscal de la lista (hoja &quot;Regimenes Fiscales&quot;)" sqref="I2:I1000">
+      <formula1>'Regimenes Fiscales'!$A$2:$A$20</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="error" errorTitle="Uso CFDI inválido" error="Seleccione un código de uso CFDI de la lista (hoja &quot;Usos CFDI&quot;)" sqref="L2:L1000">
+      <formula1>'Usos CFDI'!$A$2:$A$25</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>